--- a/files/unified_pipeline/unified_pipeline/data/results/prompt_comparison.xlsx
+++ b/files/unified_pipeline/unified_pipeline/data/results/prompt_comparison.xlsx
@@ -463,22 +463,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.1262</v>
+        <v>0.1146</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0934</v>
+        <v>0.08890000000000001</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0134</v>
+        <v>0.0129</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1753</v>
+        <v>0.1613</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8236</v>
+        <v>0.8195</v>
       </c>
       <c r="G2" t="n">
-        <v>0.3317</v>
+        <v>0.3081</v>
       </c>
     </row>
   </sheetData>
@@ -492,7 +492,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -539,22 +539,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.1249</v>
+        <v>0.1027</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0929</v>
+        <v>0.0794</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0138</v>
+        <v>0.0106</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1744</v>
+        <v>0.1559</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8231000000000001</v>
+        <v>0.8161</v>
       </c>
       <c r="G2" t="n">
-        <v>0.3317</v>
+        <v>0.296</v>
       </c>
     </row>
     <row r="3">
@@ -564,22 +564,47 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1314</v>
+        <v>0.1296</v>
       </c>
       <c r="C3" t="n">
-        <v>0.09520000000000001</v>
+        <v>0.1018</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0117</v>
+        <v>0.0172</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1789</v>
+        <v>0.1639</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8258</v>
+        <v>0.823</v>
       </c>
       <c r="G3" t="n">
-        <v>0.3316</v>
+        <v>0.3194</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>qwen_coder</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0.1347</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.1039</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.0149</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.1748</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.826</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.3323</v>
       </c>
     </row>
   </sheetData>
@@ -593,7 +618,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -636,101 +661,101 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>meta_prompting</t>
+          <t>v1_minimal</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.1331</v>
+        <v>0.1132</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0984</v>
+        <v>0.08459999999999999</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0144</v>
+        <v>0.0103</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1819</v>
+        <v>0.1715</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8306</v>
+        <v>0.8155</v>
       </c>
       <c r="G2" t="n">
-        <v>0.3518</v>
+        <v>0.305</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>self_refine</t>
+          <t>v1_minimal+meta</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1086</v>
+        <v>0.1017</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0759</v>
+        <v>0.0762</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0089</v>
+        <v>0.008200000000000001</v>
       </c>
       <c r="E3" t="n">
-        <v>0.15</v>
+        <v>0.1505</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8073</v>
+        <v>0.8089</v>
       </c>
       <c r="G3" t="n">
-        <v>0.2805</v>
+        <v>0.2794</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>v1_minimal</t>
+          <t>v2_structured</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1176</v>
+        <v>0.1311</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0847</v>
+        <v>0.1009</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0106</v>
+        <v>0.0176</v>
       </c>
       <c r="E4" t="n">
-        <v>0.171</v>
+        <v>0.1737</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8169999999999999</v>
+        <v>0.8288</v>
       </c>
       <c r="G4" t="n">
-        <v>0.3097</v>
+        <v>0.3165</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>v2_structured</t>
+          <t>v2_structured+meta</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1309</v>
+        <v>0.08309999999999999</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0993</v>
+        <v>0.0654</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0156</v>
+        <v>0.0068</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1843</v>
+        <v>0.1464</v>
       </c>
       <c r="F5" t="n">
-        <v>0.829</v>
+        <v>0.8116</v>
       </c>
       <c r="G5" t="n">
-        <v>0.3138</v>
+        <v>0.2876</v>
       </c>
     </row>
     <row r="6">
@@ -740,72 +765,147 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.1434</v>
+        <v>0.1296</v>
       </c>
       <c r="C6" t="n">
-        <v>0.1056</v>
+        <v>0.1022</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0167</v>
+        <v>0.0175</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1894</v>
+        <v>0.1722</v>
       </c>
       <c r="F6" t="n">
-        <v>0.832</v>
+        <v>0.8266</v>
       </c>
       <c r="G6" t="n">
-        <v>0.3599</v>
+        <v>0.3459</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>v4_persona</t>
+          <t>v3_template+meta</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1313</v>
+        <v>0.0866</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1013</v>
+        <v>0.0668</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0196</v>
+        <v>0.0058</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1909</v>
+        <v>0.1439</v>
       </c>
       <c r="F7" t="n">
-        <v>0.8389</v>
+        <v>0.8093</v>
       </c>
       <c r="G7" t="n">
-        <v>0.3922</v>
+        <v>0.2722</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>v4_persona</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0.1387</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.1129</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.0206</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.1763</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.8342000000000001</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.3589</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>v4_persona+meta</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.08649999999999999</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.06850000000000001</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.0074</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.1298</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.8053</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.2655</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>v5_cognitive</t>
         </is>
       </c>
-      <c r="B8" t="n">
-        <v>0.1156</v>
-      </c>
-      <c r="C8" t="n">
-        <v>0.0852</v>
-      </c>
-      <c r="D8" t="n">
-        <v>0.0069</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0.155</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0.8083</v>
-      </c>
-      <c r="G8" t="n">
-        <v>0.3054</v>
+      <c r="B10" t="n">
+        <v>0.1172</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.0893</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.009299999999999999</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.1577</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.8151</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.3219</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>v5_cognitive+meta</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>0.0737</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.053</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.0059</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.1246</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.8023</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.1687</v>
       </c>
     </row>
   </sheetData>
@@ -819,7 +919,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -876,22 +976,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.1249</v>
+        <v>0.1027</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0929</v>
+        <v>0.0794</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0138</v>
+        <v>0.0106</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1744</v>
+        <v>0.1559</v>
       </c>
       <c r="G2" t="n">
-        <v>0.8231000000000001</v>
+        <v>0.8161</v>
       </c>
       <c r="H2" t="n">
-        <v>0.3317</v>
+        <v>0.296</v>
       </c>
     </row>
     <row r="3">
@@ -901,27 +1001,52 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.1314</v>
+        <v>0.1296</v>
       </c>
       <c r="D3" t="n">
-        <v>0.09520000000000001</v>
+        <v>0.1018</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0117</v>
+        <v>0.0172</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1789</v>
+        <v>0.1639</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8258</v>
+        <v>0.823</v>
       </c>
       <c r="H3" t="n">
-        <v>0.3316</v>
+        <v>0.3194</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>qwen_coder</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>0.1347</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.1039</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.0149</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.1748</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.826</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.3323</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="A2:A4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
